--- a/vignettes/dictionary_conversion_filled_FRA.xlsx
+++ b/vignettes/dictionary_conversion_filled_FRA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="instructions" sheetId="1" state="visible" r:id="rId3"/>
@@ -4083,6 +4083,9 @@
   </sheetPr>
   <dimension ref="A1:F205"/>
   <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30.47"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
